--- a/output/第10期計画_図表データ管理台帳.xlsx
+++ b/output/第10期計画_図表データ管理台帳.xlsx
@@ -17261,7 +17261,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">

--- a/output/第10期計画_図表データ管理台帳.xlsx
+++ b/output/第10期計画_図表データ管理台帳.xlsx
@@ -4583,7 +4583,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>地域差指数による給付水準の要因分解（全国＝1.00）</a:t>
+              <a:t>地域差指数による給付水準の要素別の比較（全国＝1.00）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -6994,7 +6994,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>図18　地域差指数による給付水準の要因分解（全国＝1.00）</t>
+          <t>図18　地域差指数による給付水準の要素別の比較（全国＝1.00）</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>地域差指数による給付水準の要因分解（全国＝1.00）</t>
+          <t>地域差指数による給付水準の要素別の比較（全国＝1.00）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>地域差指数による給付水準の要因分解（全国＝1.00）</t>
+          <t>地域差指数による給付水準の要素別の比較（全国＝1.00）</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
